--- a/reference_results/tables/Table_M4_top500_model_panel_comparison.xlsx
+++ b/reference_results/tables/Table_M4_top500_model_panel_comparison.xlsx
@@ -20,10 +20,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1974" uniqueCount="59">
   <si>
-    <t>Top-500 marker-set sensitivity analysis</t>
+    <t>Supplementary Table S4. Statistical comparisons of predictive ability among models and between marker panels (primary top-500 analysis)</t>
   </si>
   <si>
-    <t>Top-500 sensitivity analysis: statistical comparison of predictive ability among M1, M2, M3 and M4-500 and between marker panels, by trait and cross-validation scheme.</t>
+    <t>Primary top-500 analysis: statistical comparison of predictive ability among M1, M2, M3 and M4-500 and between marker panels, by trait and cross-validation scheme.</t>
   </si>
   <si>
     <t>Sheet</t>
